--- a/example data/25mm/Results/ID 16 - Run 18/ID 16 - Run 18 - Standard Devs. Stepcycle.xlsx
+++ b/example data/25mm/Results/ID 16 - Run 18/ID 16 - Run 18 - Standard Devs. Stepcycle.xlsx
@@ -425,181 +425,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SC Percentages</t>
+          <t>SC Percentage</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Nose x</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Nose y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ear base x</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ear base y</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Front paw tao x</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Front paw tao y</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Wrist x</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Wrist y</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Elbow x</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Elbow y</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Lower Shoulder x</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Lower Shoulder y</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Upper Shoulder x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Upper Shoulder y</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest x</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Iliac Crest y</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Hip x</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Hip y</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Knee x</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Knee y</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle x</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Ankle y</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao x</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Hind paw tao y</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tail base x</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Tail base y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tail center x</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Tail center y</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tail tip x</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Tail tip y</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Velocity</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Acceleration</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Velocity</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Acceleration</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Velocity</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Acceleration</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Velocity</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Acceleration</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Velocity</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Acceleration</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Velocity</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Acceleration</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Velocity</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Acceleration</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Velocity</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Acceleration</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Velocity</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Acceleration</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Velocity</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Acceleration</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Velocity</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Acceleration</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Velocity</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Acceleration</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Velocity</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Acceleration</t>
         </is>
@@ -610,106 +685,151 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6634029286833443</v>
+        <v>0.8770220075568077</v>
       </c>
       <c r="C2" t="n">
+        <v>0.6634029286833418</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.797144781706685</v>
+      </c>
+      <c r="E2" t="n">
         <v>1.337550320386963</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.9261646638113089</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.4611322391965671</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.8293860577806693</v>
+        <v>4.484758138277421</v>
       </c>
       <c r="G2" t="n">
-        <v>1.121097810187672</v>
+        <v>0.9261646638113079</v>
       </c>
       <c r="H2" t="n">
-        <v>1.180592296514235</v>
+        <v>3.868115899302481</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8708950312748152</v>
+        <v>0.4611322391965679</v>
       </c>
       <c r="J2" t="n">
+        <v>3.790611994006497</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.829386057780668</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.473719433688729</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.121097810187669</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.785942105914191</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.180592296514232</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.241861054505018</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8708950312748136</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.771724559037744</v>
+      </c>
+      <c r="S2" t="n">
         <v>0.7699363554192218</v>
       </c>
-      <c r="K2" t="n">
-        <v>2.112424710619375</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="T2" t="n">
+        <v>2.523162540046052</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.11242471061937</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.392391431510949</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.17552257195308</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.722828077695365</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.134389461772377</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.205883402103259</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8.214615832930621</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>15.7534271232485</v>
-      </c>
-      <c r="R2" t="n">
-        <v>16.25033873374492</v>
-      </c>
-      <c r="S2" t="n">
-        <v>18.56170022920634</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.907507244518358</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.2294781076057647</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.593882260549752</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.572910342687066</v>
-      </c>
       <c r="X2" t="n">
-        <v>1.198626908850494</v>
+        <v>1.114425387340584</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.171775858672577</v>
+        <v>1.72282807769536</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.113704839914388</v>
+        <v>2.046800913568208</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.224231353493969</v>
+        <v>1.134389461772372</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.099991397334574</v>
+        <v>0.8363922179825261</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.203854316964241</v>
+        <v>1.205883402103253</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.412542423508845</v>
+        <v>94.21519759272024</v>
       </c>
       <c r="AE2" t="n">
-        <v>22.66718677230179</v>
+        <v>8.214615832930619</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.51633048501818</v>
+        <v>2.907507244518362</v>
       </c>
       <c r="AG2" t="n">
-        <v>20.28942604968108</v>
+        <v>0.2294781076057618</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.707261235096279</v>
+        <v>2.593882260549762</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.057039446116882</v>
+        <v>3.572910342687072</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.198626908850504</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.17177585867258</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.113704839914389</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.224231353493968</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.099991397334577</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.203854316964238</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16.17827422836602</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15.74638128305898</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>18.28991214515034</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.054687211809206</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>23.34820935487388</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>12.9887202090613</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>19.17706056420368</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>2.43139388700133</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.836431194132738</v>
       </c>
     </row>
     <row r="3">
@@ -717,106 +837,151 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8858149597523883</v>
+        <v>0.9251460418814172</v>
       </c>
       <c r="C3" t="n">
-        <v>1.12405767761057</v>
+        <v>0.8858149597523834</v>
       </c>
       <c r="D3" t="n">
-        <v>1.05588103611606</v>
+        <v>2.595852770685751</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6391369708778422</v>
+        <v>1.124057677610571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6580421677806453</v>
+        <v>4.468358494240962</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9920515454377585</v>
+        <v>1.055881036116055</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8862146489046322</v>
+        <v>3.780237995459786</v>
       </c>
       <c r="I3" t="n">
-        <v>1.307422042096169</v>
+        <v>0.6391369708778308</v>
       </c>
       <c r="J3" t="n">
-        <v>1.198613319974571</v>
+        <v>3.886292422010375</v>
       </c>
       <c r="K3" t="n">
-        <v>1.199979772372336</v>
+        <v>0.6580421677806383</v>
       </c>
       <c r="L3" t="n">
-        <v>2.702878752688859</v>
+        <v>3.452114863220327</v>
       </c>
       <c r="M3" t="n">
-        <v>1.018505588644951</v>
+        <v>0.9920515454377493</v>
       </c>
       <c r="N3" t="n">
-        <v>1.29270044427235</v>
+        <v>3.031415753176423</v>
       </c>
       <c r="O3" t="n">
-        <v>2.120586170014723</v>
+        <v>0.8862146489046365</v>
       </c>
       <c r="P3" t="n">
-        <v>4.140028058743384</v>
+        <v>2.29426597238837</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.05294600119853</v>
+        <v>1.307422042096164</v>
       </c>
       <c r="R3" t="n">
-        <v>11.22802354702406</v>
+        <v>2.677112620551677</v>
       </c>
       <c r="S3" t="n">
-        <v>6.191311586386619</v>
+        <v>1.198613319974562</v>
       </c>
       <c r="T3" t="n">
-        <v>1.074259516375581</v>
+        <v>2.828855897934739</v>
       </c>
       <c r="U3" t="n">
-        <v>1.822807336700847</v>
+        <v>1.199979772372339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.851958260168883</v>
+        <v>2.23060811017335</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7061494113423757</v>
+        <v>2.702878752688863</v>
       </c>
       <c r="X3" t="n">
+        <v>5.132380107909001</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.018505588644942</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.288159770628898</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.292700444272347</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2560183219806036</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.120586170014728</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5.353507394286852</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4.140028058743378</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.074259516375577</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.822807336700849</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.8519582601688837</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.7061494113423714</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>0.6451035854739741</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0.4682846014181318</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AK3" t="n">
+        <v>0.4682846014181314</v>
+      </c>
+      <c r="AL3" t="n">
         <v>0.3086243920589026</v>
       </c>
-      <c r="AA3" t="n">
-        <v>0.2693627785986799</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.07106865028511536</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.2068304553635614</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>5.317152509867942</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>7.992917593967985</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9.55823807705865</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>6.54370098377458</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>9.021417216752123</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.006268772926486</v>
+      <c r="AM3" t="n">
+        <v>0.269362778598674</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.07106865028511627</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.2068304553635587</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12.66261726978144</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10.64711044623289</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.937870817355751</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.432249195798954</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.141265655588823</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.172326973729552</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6.245271344369177</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.753603562987985</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.076341994522061</v>
       </c>
     </row>
     <row r="4">
@@ -824,106 +989,151 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1.086738247477549</v>
+        <v>1.12337963616432</v>
       </c>
       <c r="C4" t="n">
+        <v>1.086738247477545</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.841724965223018</v>
+      </c>
+      <c r="E4" t="n">
         <v>1.129614850741179</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.7430397175176705</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1337884461348922</v>
-      </c>
       <c r="F4" t="n">
+        <v>4.393563968092199</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7430397175176703</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.967314100564579</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.133788446134885</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.459405160349696</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.9007963895538083</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.068607667739347</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.06249134997689</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.720317793161982</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.395725603940921</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.289534389102027</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.746856517007116</v>
+        <v>3.346660844748695</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9573608830555211</v>
+        <v>1.068607667739343</v>
       </c>
       <c r="N4" t="n">
-        <v>1.747335782944788</v>
+        <v>2.955154666688078</v>
       </c>
       <c r="O4" t="n">
-        <v>3.504678473978394</v>
+        <v>1.062491349976878</v>
       </c>
       <c r="P4" t="n">
-        <v>4.63311612704037</v>
+        <v>2.956341691946055</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.019343691935039</v>
+        <v>1.72031779316198</v>
       </c>
       <c r="R4" t="n">
-        <v>14.51668734309524</v>
+        <v>2.925559489933715</v>
       </c>
       <c r="S4" t="n">
-        <v>2.328504176869461</v>
+        <v>1.39572560394092</v>
       </c>
       <c r="T4" t="n">
-        <v>1.274227265648474</v>
+        <v>3.648288793891239</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5078812306080916</v>
+        <v>1.289534389102036</v>
       </c>
       <c r="V4" t="n">
-        <v>0.723887363542152</v>
+        <v>3.110005724217985</v>
       </c>
       <c r="W4" t="n">
-        <v>0.522917744572833</v>
+        <v>1.746856517007118</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4969159343321316</v>
+        <v>3.709301711083157</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03515840564959989</v>
+        <v>0.9573608830555209</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.7209193869544624</v>
+        <v>2.343554697791967</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3197685957903872</v>
+        <v>1.747335782944787</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4252601009003963</v>
+        <v>0.86410908759298</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.3338832304475401</v>
+        <v>3.504678473978393</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.148857493439345</v>
+        <v>51.25286870905521</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.845164319721885</v>
+        <v>4.633116127040362</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.029461968263079</v>
+        <v>1.274227265648476</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.875893339793655</v>
+        <v>0.5078812306080918</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.827819477525021</v>
+        <v>0.7238873635421496</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.986336902004849</v>
+        <v>0.5229177445728286</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4969159343321324</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.03515840564960513</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.720919386954459</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.3197685957903879</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.4252601009003953</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.3338832304475399</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.54103982233699</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13.96780110555344</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.24333441161303</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.318758055201416</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.800166148085443</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.9405599845886577</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.770368723316025</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.688683161099358</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.894429272585824</v>
       </c>
     </row>
     <row r="5">
@@ -931,106 +1141,151 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>1.815468773799568</v>
+        <v>29.90973584133602</v>
       </c>
       <c r="C5" t="n">
-        <v>1.325262278997897</v>
+        <v>1.815468773799555</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9073280254347541</v>
+        <v>2.989782714229013</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3269748044391786</v>
+        <v>1.325262278997895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9910745809530933</v>
+        <v>4.523055581234465</v>
       </c>
       <c r="G5" t="n">
-        <v>1.318935078996177</v>
+        <v>0.9073280254347458</v>
       </c>
       <c r="H5" t="n">
-        <v>1.090136992934048</v>
+        <v>3.881021223178678</v>
       </c>
       <c r="I5" t="n">
-        <v>1.687330402041386</v>
+        <v>0.3269748044391744</v>
       </c>
       <c r="J5" t="n">
-        <v>1.140568244718222</v>
+        <v>3.392825165490841</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6542328385215662</v>
+        <v>0.991074580953079</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6470700776279017</v>
+        <v>3.354368133392706</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5397238239176981</v>
+        <v>1.318935078996171</v>
       </c>
       <c r="N5" t="n">
-        <v>1.899985106384835</v>
+        <v>3.019257757521777</v>
       </c>
       <c r="O5" t="n">
-        <v>3.943476852975797</v>
+        <v>1.090136992934037</v>
       </c>
       <c r="P5" t="n">
-        <v>4.666377554401152</v>
+        <v>3.0853893884443</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.246060089879889</v>
+        <v>1.687330402041385</v>
       </c>
       <c r="R5" t="n">
-        <v>7.969198189008228</v>
+        <v>3.529842651027534</v>
       </c>
       <c r="S5" t="n">
-        <v>6.204690472959584</v>
+        <v>1.140568244718218</v>
       </c>
       <c r="T5" t="n">
-        <v>1.199484543683941</v>
+        <v>3.931491679388426</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2753517932122616</v>
+        <v>0.6542328385215694</v>
       </c>
       <c r="V5" t="n">
-        <v>1.162844195787812</v>
+        <v>2.688536653984498</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3404822473739216</v>
+        <v>0.6470700776278928</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4952196107295082</v>
+        <v>2.962862692440819</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.343214810092586</v>
+        <v>0.539723823917697</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7187585195541065</v>
+        <v>2.45876061008628</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.336096261039024</v>
+        <v>1.899985106384829</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4912528907432823</v>
+        <v>1.567722190807582</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1098252170051973</v>
+        <v>3.943476852975789</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.39595448576573</v>
+        <v>1.770273412968235</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.033322959820399</v>
+        <v>4.666377554401155</v>
       </c>
       <c r="AF5" t="n">
-        <v>5.761067958486788</v>
+        <v>1.199484543683943</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2630192060714463</v>
+        <v>0.2753517932122631</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.370450320934287</v>
+        <v>1.162844195787816</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.59609197513738</v>
+        <v>0.3404822473739225</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.4952196107295203</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.3432148100925917</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.7187585195541097</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.3360962610390262</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.4912528907432828</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.1098252170051961</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.074447325347458</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.749188399965169</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.210995260486473</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.470587983294212</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.029911215257446</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.54469141521941</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.2755872067317868</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.276994062136485</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.529721793652865</v>
       </c>
     </row>
     <row r="6">
@@ -1038,106 +1293,151 @@
         <v>20</v>
       </c>
       <c r="B6" t="n">
-        <v>1.294961113294767</v>
+        <v>28.86141215633695</v>
       </c>
       <c r="C6" t="n">
-        <v>1.279114502425059</v>
+        <v>1.29496111329477</v>
       </c>
       <c r="D6" t="n">
-        <v>0.757350432949246</v>
+        <v>2.90287961142166</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2058546133675768</v>
+        <v>1.279114502425062</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2676937161559276</v>
+        <v>4.458591160024127</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8798655314762184</v>
+        <v>0.7573504329492421</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8680064724579971</v>
+        <v>3.681296648148554</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8446904741478123</v>
+        <v>0.2058546133675731</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6657851456700219</v>
+        <v>3.051832167470824</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5355308016784762</v>
+        <v>0.2676937161559294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5317499516354586</v>
+        <v>3.02803313494883</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4919011350631462</v>
+        <v>0.8798655314762216</v>
       </c>
       <c r="N6" t="n">
-        <v>1.230472890024898</v>
+        <v>2.657688913038679</v>
       </c>
       <c r="O6" t="n">
-        <v>3.50955775495816</v>
+        <v>0.8680064724579938</v>
       </c>
       <c r="P6" t="n">
-        <v>19.92516288275391</v>
+        <v>3.221810808172449</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.256374566066949</v>
+        <v>0.8446904741478175</v>
       </c>
       <c r="R6" t="n">
-        <v>3.400678083788083</v>
+        <v>3.88340960169744</v>
       </c>
       <c r="S6" t="n">
-        <v>7.718938763612651</v>
+        <v>0.6657851456700244</v>
       </c>
       <c r="T6" t="n">
+        <v>4.033860920189713</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5355308016784808</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.328184261055874</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5317499516354545</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.338709106885647</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4919011350631518</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.108022754415031</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.230472890024904</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.483695996808074</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.509557754958163</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>61.34769990894665</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>19.9251628827539</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.021230895436702</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.5877452946989287</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.8835877101937172</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.4292962848803482</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.5423966415723779</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.2574211038184625</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.3814022497641072</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.3369656219409841</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.3574904910620715</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.285075116862791</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.80562919891029</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.065056195826237</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.708112757599852</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.152227530866915</v>
+        <v>0.5877452946989374</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.337541106734973</v>
+        <v>0.8835877101937156</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.790780000866042</v>
+        <v>0.4292962848803468</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.5423966415723727</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.2574211038184751</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.3814022497641044</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.3369656219409812</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.3574904910620711</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.285075116862778</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8.308653850079613</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.309644087719269</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7.598824706695427</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.791293038375634</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.110437730401936</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.691444812095985</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.052685626130863</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.377054704848013</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.671309250951033</v>
       </c>
     </row>
     <row r="7">
@@ -1145,106 +1445,151 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>1.47398547015871</v>
+        <v>29.53036705267741</v>
       </c>
       <c r="C7" t="n">
-        <v>1.602930068436346</v>
+        <v>1.473985470158714</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3246125696176839</v>
+        <v>3.227911574824026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.242578782417986</v>
+        <v>1.602930068436349</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6293050886804291</v>
+        <v>4.000551028989208</v>
       </c>
       <c r="G7" t="n">
-        <v>1.132927985947111</v>
+        <v>0.324612569617691</v>
       </c>
       <c r="H7" t="n">
-        <v>1.090935494261911</v>
+        <v>3.414600181206172</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5851488771097644</v>
+        <v>0.2425787824179829</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6655133078402085</v>
+        <v>3.41118658767099</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6111771471953987</v>
+        <v>0.629305088680431</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4491205828725369</v>
+        <v>3.203919204176653</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2493423368934119</v>
+        <v>1.132927985947102</v>
       </c>
       <c r="N7" t="n">
-        <v>1.157340976722569</v>
+        <v>2.712738229037515</v>
       </c>
       <c r="O7" t="n">
+        <v>1.090935494261902</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.82777241284414</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5851488771097614</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.275652789062498</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6655133078402045</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.646399323786395</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.6111771471953927</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.968946327978735</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.4491205828725358</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.936097947653628</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.2493423368934077</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.634844163002896</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.157340976722568</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.572002387417253</v>
+      </c>
+      <c r="AC7" t="n">
         <v>3.205193763772415</v>
       </c>
-      <c r="P7" t="n">
-        <v>3.416759718681997</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7.79590020680511</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.0901602048506</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.410161920547932</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.3341506150819589</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.3726347227477814</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.5801726385323275</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.4467751458291584</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.1124970260991741</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.3134751174656247</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.1646630349454132</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.3025694456482496</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.3822237112957279</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.2046439329421358</v>
-      </c>
       <c r="AD7" t="n">
-        <v>3.259793925076391</v>
+        <v>0.2529156639094514</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.216154260067954</v>
+        <v>3.416759718682</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.064344459047205</v>
+        <v>0.3341506150819478</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.225101404548189</v>
+        <v>0.3726347227477915</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.422065335040123</v>
+        <v>0.5801726385323308</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.9914438068479928</v>
+        <v>0.4467751458291601</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1124970260991762</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.3134751174656213</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1646630349454154</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.302569445648241</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.382223711295724</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.2046439329421313</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.820367182560779</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.054325476422755</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.386467505623251</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.279176850966346</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.212799543037001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.080053561337306</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.206096163315172</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.357222780545837</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.9375133215747048</v>
       </c>
     </row>
     <row r="8">
@@ -1252,106 +1597,151 @@
         <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>1.464026947129809</v>
+        <v>30.87409785016638</v>
       </c>
       <c r="C8" t="n">
-        <v>1.545526786362647</v>
+        <v>1.464026947129803</v>
       </c>
       <c r="D8" t="n">
-        <v>2.250502937093633</v>
+        <v>4.51395187628593</v>
       </c>
       <c r="E8" t="n">
-        <v>1.716938811832259</v>
+        <v>1.545526786362645</v>
       </c>
       <c r="F8" t="n">
-        <v>1.708194192860369</v>
+        <v>6.479053319315099</v>
       </c>
       <c r="G8" t="n">
-        <v>1.320179675183158</v>
+        <v>2.250502937093634</v>
       </c>
       <c r="H8" t="n">
-        <v>1.285446346929893</v>
+        <v>6.970082007837548</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9492181732327261</v>
+        <v>1.71693881183226</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9430174170680325</v>
+        <v>4.79874646383944</v>
       </c>
       <c r="K8" t="n">
-        <v>1.112797120992089</v>
+        <v>1.708194192860363</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8518726552028308</v>
+        <v>4.725488893740846</v>
       </c>
       <c r="M8" t="n">
-        <v>0.690492047610717</v>
+        <v>1.320179675183154</v>
       </c>
       <c r="N8" t="n">
-        <v>1.068407362548544</v>
+        <v>4.251575204736008</v>
       </c>
       <c r="O8" t="n">
-        <v>2.732525995408214</v>
+        <v>1.285446346929886</v>
       </c>
       <c r="P8" t="n">
-        <v>2.947595965891253</v>
+        <v>4.554413492806056</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.323173220347025</v>
+        <v>0.9492181732327223</v>
       </c>
       <c r="R8" t="n">
-        <v>4.10183192746787</v>
+        <v>4.649509523519891</v>
       </c>
       <c r="S8" t="n">
-        <v>1.410566805181514</v>
+        <v>0.9430174170680283</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2655152346374689</v>
+        <v>4.92781847677716</v>
       </c>
       <c r="U8" t="n">
-        <v>0.109988885872083</v>
+        <v>1.112797120992093</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1938310626352478</v>
+        <v>4.22237359502882</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3904876979164163</v>
+        <v>0.8518726552028282</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1082293930037127</v>
+        <v>5.352002525668413</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1109942468752493</v>
+        <v>0.6904920476107131</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2083585158882927</v>
+        <v>3.393924846735491</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03043357147078986</v>
+        <v>1.068407362548542</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.05899284278112466</v>
+        <v>2.2889443505969</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2242778902856112</v>
+        <v>2.732525995408218</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.9279787604138346</v>
+        <v>1.613067551272565</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.389127388678212</v>
+        <v>2.947595965891249</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.8725215774152315</v>
+        <v>0.2655152346374551</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.9248537785769363</v>
+        <v>0.1099888858720758</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.208676972289049</v>
+        <v>0.1938310626352457</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.336927316096892</v>
+        <v>0.3904876979164165</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.1082293930037131</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.1109942468752486</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2083585158882867</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.03043357147079557</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.05899284278111125</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.224277890285604</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.274823797660915</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.031154206119801</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.490643603691043</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.9423327155765089</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.405926018805783</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.8976780795348521</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.952320184862278</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.132495534404412</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.3390911268639674</v>
       </c>
     </row>
     <row r="9">
@@ -1359,106 +1749,151 @@
         <v>32</v>
       </c>
       <c r="B9" t="n">
-        <v>1.325566611988748</v>
+        <v>31.64997663129924</v>
       </c>
       <c r="C9" t="n">
-        <v>1.266727009464698</v>
+        <v>1.325566611988749</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5380068278196792</v>
+        <v>5.602498449195832</v>
       </c>
       <c r="E9" t="n">
-        <v>1.187348524097986</v>
+        <v>1.266727009464694</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5241233173955534</v>
+        <v>11.35304215182926</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8393812921026386</v>
+        <v>0.5380068278196836</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8281426037536693</v>
+        <v>9.87285014870959</v>
       </c>
       <c r="I9" t="n">
-        <v>1.390742315225022</v>
+        <v>1.187348524097987</v>
       </c>
       <c r="J9" t="n">
+        <v>6.208663351541746</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.524123317395556</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.101931536863084</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.8393812921026395</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.270323333315907</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8281426037536768</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.119051660618382</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.390742315225029</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5.043617342223787</v>
+      </c>
+      <c r="S9" t="n">
         <v>1.108832596122477</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.9905657501092892</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4674985944625413</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.1426643852813736</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.07449112522699</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="T9" t="n">
+        <v>5.389078135584001</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.9905657501092836</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.375228154530856</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.4674985944625378</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5.398053169081291</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.1426643852813811</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.497624606647017</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.074491125226994</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.300641524477239</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.799597757641492</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.881687420232489</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10.8823728876703</v>
-      </c>
-      <c r="R9" t="n">
-        <v>5.758728005643445</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.8812506361691951</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.1373596918419629</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1615213679961421</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.1534506689384019</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.04669368303500252</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.2050239407570324</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.149262961863002</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.1552933890379795</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.1754255997702033</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.2924572268386299</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.114027091636581</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.206169176321616</v>
+        <v>2.710956206151451</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.7383463143310182</v>
+        <v>2.881687420232482</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.7971432143314442</v>
+        <v>0.1373596918419761</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.177768612877659</v>
+        <v>0.1615213679961275</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.059299971083252</v>
+        <v>0.1534506689383988</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.511849043023059</v>
+        <v>0.04669368303500086</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.2050239407570478</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.1492629618629917</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1552933890379919</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.1754255997702008</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.2924572268386202</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.1140270916365646</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10.73174513509715</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.599312411392842</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.035488766317591</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.216387712950588</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.739462869064655</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.8200384853078149</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.156965845258979</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.038697800183155</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.473799420932244</v>
       </c>
     </row>
     <row r="10">
@@ -1466,106 +1901,151 @@
         <v>36</v>
       </c>
       <c r="B10" t="n">
-        <v>1.280128259142197</v>
+        <v>32.65295927973323</v>
       </c>
       <c r="C10" t="n">
-        <v>1.240595660339668</v>
+        <v>1.280128259142195</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8889893864735803</v>
+        <v>6.294580872566478</v>
       </c>
       <c r="E10" t="n">
-        <v>0.418525576749066</v>
+        <v>1.240595660339677</v>
       </c>
       <c r="F10" t="n">
-        <v>0.905932338781723</v>
+        <v>13.6315664708531</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8036317712128244</v>
+        <v>0.8889893864735874</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7971252111972063</v>
+        <v>10.16045956434086</v>
       </c>
       <c r="I10" t="n">
-        <v>1.600526563707918</v>
+        <v>0.4185255767490713</v>
       </c>
       <c r="J10" t="n">
-        <v>1.483575630551149</v>
+        <v>7.25142021570435</v>
       </c>
       <c r="K10" t="n">
-        <v>1.725993888412706</v>
+        <v>0.9059323387817172</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8327382720244424</v>
+        <v>6.607799267678109</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4746868047536952</v>
+        <v>0.8036317712128314</v>
       </c>
       <c r="N10" t="n">
-        <v>1.025302479223056</v>
+        <v>5.792774129246107</v>
       </c>
       <c r="O10" t="n">
-        <v>2.975248026723486</v>
+        <v>0.7971252111972084</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25281693023959</v>
+        <v>5.67932307905867</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.77175597236249</v>
+        <v>1.600526563707915</v>
       </c>
       <c r="R10" t="n">
-        <v>4.590061751159782</v>
+        <v>5.700469057553089</v>
       </c>
       <c r="S10" t="n">
-        <v>3.215581190401164</v>
+        <v>1.483575630551141</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07154225405534252</v>
+        <v>5.73275784065225</v>
       </c>
       <c r="U10" t="n">
-        <v>0.101822919648896</v>
+        <v>1.725993888412694</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1297312972312089</v>
+        <v>4.482672475243262</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03554813517530579</v>
+        <v>0.8327382720244372</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3536092048109736</v>
+        <v>5.50143808677234</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1622761818026817</v>
+        <v>0.474686804753688</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1796055465318017</v>
+        <v>5.230647867070072</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.06266878820930638</v>
+        <v>1.025302479223045</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2056199226625475</v>
+        <v>4.496459632692857</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.06467896589290917</v>
+        <v>2.975248026723475</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.562602942137311</v>
+        <v>3.50304183117784</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.123303500304503</v>
+        <v>3.252816930239582</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.24165541690602</v>
+        <v>0.07154225405533685</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.6586958094490865</v>
+        <v>0.1018229196489002</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.691628953972219</v>
+        <v>0.1297312972312042</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.5860481155757081</v>
+        <v>0.03554813517530728</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.3536092048109575</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.162276181802694</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1796055465318014</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.06266878820930141</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.2056199226625295</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.06467896589290337</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>12.54775794900587</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.436278306532595</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.163907662121813</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.5538041097001619</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.088817052700542</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.18218723840257</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.6127526555708993</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.625320219772166</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.5829744507534886</v>
       </c>
     </row>
     <row r="11">
@@ -1573,106 +2053,151 @@
         <v>40</v>
       </c>
       <c r="B11" t="n">
-        <v>2.301447434645763</v>
+        <v>33.26665929059487</v>
       </c>
       <c r="C11" t="n">
-        <v>1.75085214628294</v>
+        <v>2.301447434645768</v>
       </c>
       <c r="D11" t="n">
-        <v>1.720712217542861</v>
+        <v>7.240943985620747</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8271777378710659</v>
+        <v>1.750852146282942</v>
       </c>
       <c r="F11" t="n">
-        <v>1.145011437896265</v>
+        <v>12.065634368426</v>
       </c>
       <c r="G11" t="n">
-        <v>1.498408101887528</v>
+        <v>1.720712217542863</v>
       </c>
       <c r="H11" t="n">
-        <v>1.065395152709478</v>
+        <v>10.97343135255665</v>
       </c>
       <c r="I11" t="n">
-        <v>1.092943789792839</v>
+        <v>0.8271777378710752</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8668287242870856</v>
+        <v>9.035651214694797</v>
       </c>
       <c r="K11" t="n">
-        <v>1.665115622023944</v>
+        <v>1.145011437896268</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7204957133050426</v>
+        <v>7.614830911853178</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1831007165063347</v>
+        <v>1.498408101887531</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6214738022297722</v>
+        <v>7.065390849010828</v>
       </c>
       <c r="O11" t="n">
-        <v>2.152586461620867</v>
+        <v>1.065395152709484</v>
       </c>
       <c r="P11" t="n">
-        <v>2.683445998197056</v>
+        <v>6.071481835111596</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.33923007302822</v>
+        <v>1.092943789792841</v>
       </c>
       <c r="R11" t="n">
-        <v>2.366072405748249</v>
+        <v>5.964009068722412</v>
       </c>
       <c r="S11" t="n">
-        <v>5.374241850077097</v>
+        <v>0.8668287242870736</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1118016791205019</v>
+        <v>5.781308489368702</v>
       </c>
       <c r="U11" t="n">
-        <v>0.05265092618968314</v>
+        <v>1.665115622023946</v>
       </c>
       <c r="V11" t="n">
-        <v>0.07897909068852217</v>
+        <v>4.576908415240102</v>
       </c>
       <c r="W11" t="n">
-        <v>0.06150883249770597</v>
+        <v>0.7204957133050434</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2306257888669704</v>
+        <v>5.327270899980295</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2711578896942483</v>
+        <v>0.1831007165063312</v>
       </c>
       <c r="Z11" t="n">
+        <v>5.742220790434345</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.6214738022297684</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.522316111674275</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.152586461620865</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.899902206420432</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.683445998197051</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1118016791204993</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.05265092618967129</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.07897909068851899</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.06150883249770795</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.2306257888669708</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.2711578896942334</v>
+      </c>
+      <c r="AL11" t="n">
         <v>0.3286262417794218</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0.0391790332857942</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.2956414903521952</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.02757559120645062</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.214305001052081</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.003727350893227</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.416472505931448</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.557990260923801</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.697823812104917</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.366368530013849</v>
+      <c r="AM11" t="n">
+        <v>0.03917903328580018</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.2956414903521984</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.02757559120644031</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>12.12610652582334</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.200202540592601</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.14473826120498</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.178144106892516</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.9782078651902674</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.355969021613246</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.467836162566404</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.6400978443987263</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.26531981718235</v>
       </c>
     </row>
     <row r="12">
@@ -1680,106 +2205,151 @@
         <v>44</v>
       </c>
       <c r="B12" t="n">
-        <v>2.688274922673998</v>
+        <v>34.04740345572166</v>
       </c>
       <c r="C12" t="n">
-        <v>1.921676903919849</v>
+        <v>2.688274922674005</v>
       </c>
       <c r="D12" t="n">
-        <v>0.845269462580826</v>
+        <v>7.902187488028406</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9758262653286913</v>
+        <v>1.921676903919855</v>
       </c>
       <c r="F12" t="n">
-        <v>1.390009520906983</v>
+        <v>11.07411620997674</v>
       </c>
       <c r="G12" t="n">
-        <v>1.751864620229901</v>
+        <v>0.8452694625808239</v>
       </c>
       <c r="H12" t="n">
-        <v>1.652958380097293</v>
+        <v>10.28258684222919</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8569720356724312</v>
+        <v>0.9758262653286817</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9130028867230283</v>
+        <v>8.733370888506576</v>
       </c>
       <c r="K12" t="n">
-        <v>1.349073297699065</v>
+        <v>1.390009520906969</v>
       </c>
       <c r="L12" t="n">
-        <v>0.726543881470132</v>
+        <v>8.063424888075895</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2912384938259118</v>
+        <v>1.751864620229903</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3074400622644276</v>
+        <v>7.868006641177053</v>
       </c>
       <c r="O12" t="n">
-        <v>1.973506089192875</v>
+        <v>1.652958380097288</v>
       </c>
       <c r="P12" t="n">
-        <v>2.917988866438222</v>
+        <v>6.072545357662994</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.33231882259135</v>
+        <v>0.8569720356724473</v>
       </c>
       <c r="R12" t="n">
-        <v>4.99112657018678</v>
+        <v>5.891260348040967</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94058690481713</v>
+        <v>0.9130028867230339</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04600522380305203</v>
+        <v>5.639784457320651</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03140864194875441</v>
+        <v>1.349073297699074</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09345598425907875</v>
+        <v>4.578151734153907</v>
       </c>
       <c r="W12" t="n">
-        <v>0.06857001720183759</v>
+        <v>0.7265438814701377</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2363130193779544</v>
+        <v>5.293769603564996</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1249986609560358</v>
+        <v>0.2912384938259042</v>
       </c>
       <c r="Z12" t="n">
+        <v>5.96748198643103</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.3074400622644304</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.122170326154477</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.973506089192882</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.274074638098407</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.917988866438231</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.04600522380304124</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.03140864194874868</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.0934559842590722</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.06857001720183853</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.2363130193779394</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.1249986609560378</v>
+      </c>
+      <c r="AL12" t="n">
         <v>0.1808457044473827</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0.2591009922657957</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.2283266126024306</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.07396363637209237</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.068093319960098</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.072026376390244</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.996125131293369</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.305034814277567</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.222719361113064</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.407022320572509</v>
+      <c r="AM12" t="n">
+        <v>0.2591009922658024</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.2283266126024376</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.07396363637208971</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10.05550180033637</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.886317455992844</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.931877270718663</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.071380676439554</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.029254662813518</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.876643129833946</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.24952662691391</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.095481933766801</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.309224348961768</v>
       </c>
     </row>
     <row r="13">
@@ -1787,106 +2357,151 @@
         <v>48</v>
       </c>
       <c r="B13" t="n">
-        <v>2.604069471011484</v>
+        <v>34.9924149335972</v>
       </c>
       <c r="C13" t="n">
-        <v>2.047408991138803</v>
+        <v>2.604069471011487</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4488695138480184</v>
+        <v>8.404373552892597</v>
       </c>
       <c r="E13" t="n">
-        <v>1.007499012463901</v>
+        <v>2.047408991138806</v>
       </c>
       <c r="F13" t="n">
-        <v>1.369024474679807</v>
+        <v>10.14615251860519</v>
       </c>
       <c r="G13" t="n">
-        <v>1.821088541509535</v>
+        <v>0.4488695138480258</v>
       </c>
       <c r="H13" t="n">
-        <v>1.540310499693195</v>
+        <v>9.815553114187976</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4684705837001023</v>
+        <v>1.007499012463909</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3276930176335299</v>
+        <v>8.869181242008917</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3162368629229911</v>
+        <v>1.369024474679818</v>
       </c>
       <c r="L13" t="n">
-        <v>1.290874377982931</v>
+        <v>7.691546185451869</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9895255568069653</v>
+        <v>1.821088541509536</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2819877653749238</v>
+        <v>7.902894198772938</v>
       </c>
       <c r="O13" t="n">
-        <v>1.331187820856687</v>
+        <v>1.540310499693199</v>
       </c>
       <c r="P13" t="n">
-        <v>2.226150642531004</v>
+        <v>6.000373109687719</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.042343226522023</v>
+        <v>0.4684705837001015</v>
       </c>
       <c r="R13" t="n">
-        <v>6.971489907129397</v>
+        <v>5.973957731281581</v>
       </c>
       <c r="S13" t="n">
-        <v>3.361452718023817</v>
+        <v>0.3276930176335316</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07637030875599632</v>
+        <v>5.791725329622676</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0581014945271783</v>
+        <v>0.3162368629229942</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1138380961580296</v>
+        <v>4.680596926436002</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1123529126488256</v>
+        <v>1.290874377982934</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1043298212676814</v>
+        <v>5.359350054209348</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1853524026021565</v>
+        <v>0.989525556806957</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.1317637171227728</v>
+        <v>5.944008714597794</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.08698307550905769</v>
+        <v>0.2819877653749198</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1648219576918022</v>
+        <v>4.505964853493958</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0617066979601745</v>
+        <v>1.331187820856688</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5149517890387244</v>
+        <v>3.854224343726093</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.779227106943554</v>
+        <v>2.226150642531013</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.210973215304432</v>
+        <v>0.07637030875599755</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.879155983455302</v>
+        <v>0.05810149452717586</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.221840823637484</v>
+        <v>0.1138380961580281</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.033957509294698</v>
+        <v>0.1123529126488227</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.1043298212676789</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.1853524026021431</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.131763717122779</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.08698307550905905</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.1648219576918134</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.06170669796018248</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.735822604560834</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>6.782467933714478</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.366689204405156</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.4824184114347527</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.735787905625328</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.155678691754605</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.807245348608558</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.153570801862994</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.943923737137217</v>
       </c>
     </row>
     <row r="14">
@@ -1894,106 +2509,151 @@
         <v>52</v>
       </c>
       <c r="B14" t="n">
-        <v>10.67356245868439</v>
+        <v>13.85008851894013</v>
       </c>
       <c r="C14" t="n">
-        <v>7.351242863825422</v>
+        <v>10.6735624586844</v>
       </c>
       <c r="D14" t="n">
+        <v>39.97303707257925</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.351242863825421</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13.83213030287955</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.5294812956784233</v>
       </c>
-      <c r="E14" t="n">
-        <v>1.437802636622561</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.368062864494642</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.577417123276206</v>
-      </c>
       <c r="H14" t="n">
-        <v>1.402622193005429</v>
+        <v>9.697445364681515</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6597057606622462</v>
+        <v>1.437802636622568</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6071196812675824</v>
+        <v>9.205738551150624</v>
       </c>
       <c r="K14" t="n">
-        <v>1.216355746797836</v>
+        <v>1.368062864494644</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9295968403498998</v>
+        <v>8.212607014341042</v>
       </c>
       <c r="M14" t="n">
-        <v>0.38492226121678</v>
+        <v>1.577417123276208</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2978541098190962</v>
+        <v>7.975279137176356</v>
       </c>
       <c r="O14" t="n">
-        <v>1.512159125928819</v>
+        <v>1.402622193005425</v>
       </c>
       <c r="P14" t="n">
-        <v>2.379840977520051</v>
+        <v>5.892205180369674</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.69398802752267</v>
+        <v>0.6597057606622427</v>
       </c>
       <c r="R14" t="n">
-        <v>4.842252603679776</v>
+        <v>6.150445587401826</v>
       </c>
       <c r="S14" t="n">
-        <v>8.869485704258031</v>
+        <v>0.6071196812675856</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1410743677070889</v>
+        <v>5.738699839829916</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02874090221152298</v>
+        <v>1.216355746797827</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2437681699780337</v>
+        <v>4.371851914252195</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1449132947778102</v>
+        <v>0.9295968403499094</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1535368180155268</v>
+        <v>5.188105056440086</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1047677475979606</v>
+        <v>0.3849222612167942</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1797533755218286</v>
+        <v>5.978522414111774</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.1655375110831572</v>
+        <v>0.2978541098190952</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.106625521855453</v>
+        <v>4.737926508348667</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1077968231006089</v>
+        <v>1.512159125928812</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.129033800760073</v>
+        <v>3.947535158319023</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.282367735381652</v>
+        <v>2.379840977520052</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.777049196099887</v>
+        <v>0.1410743677070914</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.236613885715858</v>
+        <v>0.02874090221152932</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.071139799502478</v>
+        <v>0.2437681699780325</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.355046849423424</v>
+        <v>0.1449132947778031</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.1535368180155162</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.1047677475979576</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.1797533755218183</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.1655375110831537</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.1066255218554474</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.1077968231006214</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.27176892162241</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.59723887903789</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.719512984825109</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.096821882834648</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.234306841179817</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.749463913895561</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.178942501186759</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.987451061939337</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.274187487532582</v>
       </c>
     </row>
     <row r="15">
@@ -2001,106 +2661,151 @@
         <v>56</v>
       </c>
       <c r="B15" t="n">
+        <v>14.00734559690736</v>
+      </c>
+      <c r="C15" t="n">
         <v>10.6886524142313</v>
       </c>
-      <c r="C15" t="n">
-        <v>4.254569775327892</v>
-      </c>
       <c r="D15" t="n">
-        <v>0.5382550982875323</v>
+        <v>37.93593611573034</v>
       </c>
       <c r="E15" t="n">
-        <v>0.52875930778729</v>
+        <v>4.254569775327897</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9841922670691384</v>
+        <v>14.30081577696655</v>
       </c>
       <c r="G15" t="n">
-        <v>1.455475135400342</v>
+        <v>0.5382550982875294</v>
       </c>
       <c r="H15" t="n">
-        <v>1.391557624753271</v>
+        <v>11.42159154061237</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3573638586968543</v>
+        <v>0.5287593077872866</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2145879543172669</v>
+        <v>8.35878972374099</v>
       </c>
       <c r="K15" t="n">
-        <v>1.032655676159712</v>
+        <v>0.9841922670691275</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8261267912949785</v>
+        <v>7.912166230433626</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5792325713328432</v>
+        <v>1.455475135400351</v>
       </c>
       <c r="N15" t="n">
-        <v>0.208829770858783</v>
+        <v>7.667838668752526</v>
       </c>
       <c r="O15" t="n">
-        <v>0.866248847287411</v>
+        <v>1.391557624753275</v>
       </c>
       <c r="P15" t="n">
-        <v>1.508910300386156</v>
+        <v>5.901794367772207</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.402786106281754</v>
+        <v>0.3573638586968488</v>
       </c>
       <c r="R15" t="n">
-        <v>3.572694254794439</v>
+        <v>6.221142821748782</v>
       </c>
       <c r="S15" t="n">
-        <v>9.375599048186958</v>
+        <v>0.2145879543172756</v>
       </c>
       <c r="T15" t="n">
-        <v>0.08066572472924707</v>
+        <v>5.642614356407607</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06332985304758493</v>
+        <v>1.032655676159713</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2427077692475123</v>
+        <v>4.400954843419735</v>
       </c>
       <c r="W15" t="n">
-        <v>0.182696321614666</v>
+        <v>0.826126791294982</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1883181016809027</v>
+        <v>5.211223562121051</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.09562161295818686</v>
+        <v>0.5792325713328467</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2806903178633529</v>
+        <v>6.032153638870392</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1756886317448084</v>
+        <v>0.2088297708587804</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.05694816551682452</v>
+        <v>5.128455900420137</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1320822517023379</v>
+        <v>0.8662488472874046</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.461858153215176</v>
+        <v>4.258646146745579</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.998917013886201</v>
+        <v>1.508910300386142</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.714434355398269</v>
+        <v>0.0806657247292417</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.004195865948696</v>
+        <v>0.06332985304758423</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.638812443729088</v>
+        <v>0.2427077692474987</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.948655469210939</v>
+        <v>0.1826963216146633</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.1883181016809007</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.09562161295819381</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.2806903178633379</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.1756886317448086</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.05694816551683955</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.1320822517023332</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9.036095094979672</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.282325240819632</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.219445994086522</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.444085426039927</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.955615638926931</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.688942653420298</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.9788589519077922</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.541600799767151</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.904120408498973</v>
       </c>
     </row>
     <row r="16">
@@ -2108,106 +2813,151 @@
         <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>11.26546303192728</v>
+        <v>79.88189145228668</v>
       </c>
       <c r="C16" t="n">
-        <v>3.988626205446444</v>
+        <v>11.26546303192729</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4292360016492617</v>
+        <v>35.81935482886188</v>
       </c>
       <c r="E16" t="n">
-        <v>11.08280906393086</v>
+        <v>3.988626205446442</v>
       </c>
       <c r="F16" t="n">
-        <v>1.272271631714586</v>
+        <v>14.40256714191484</v>
       </c>
       <c r="G16" t="n">
-        <v>1.371463564354328</v>
+        <v>0.4292360016492658</v>
       </c>
       <c r="H16" t="n">
-        <v>1.135968849906958</v>
+        <v>71.12496237460111</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7887068799679857</v>
+        <v>11.08280906393087</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4065961414242351</v>
+        <v>7.70151765018967</v>
       </c>
       <c r="K16" t="n">
-        <v>1.295544689354533</v>
+        <v>1.272271631714591</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6349896004562272</v>
+        <v>7.745109634558482</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2423366927071383</v>
+        <v>1.371463564354334</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4233679591151963</v>
+        <v>6.890575942840109</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9060560943103213</v>
+        <v>1.135968849906961</v>
       </c>
       <c r="P16" t="n">
-        <v>1.681013035314934</v>
+        <v>5.894729804281155</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.176507230735034</v>
+        <v>0.7887068799679796</v>
       </c>
       <c r="R16" t="n">
-        <v>1.708153395115882</v>
+        <v>6.173136056342229</v>
       </c>
       <c r="S16" t="n">
-        <v>10.0060279234286</v>
+        <v>0.4065961414242427</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0331872800450177</v>
+        <v>5.425887909012264</v>
       </c>
       <c r="U16" t="n">
-        <v>0.06918036668135089</v>
+        <v>1.295544689354528</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1330834678444316</v>
+        <v>4.688418535831784</v>
       </c>
       <c r="W16" t="n">
-        <v>0.06710002900441352</v>
+        <v>0.6349896004562243</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3391089227559346</v>
+        <v>5.189679022498342</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.02677780589124579</v>
+        <v>0.2423366927071348</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1949306916753682</v>
+        <v>6.338789431921599</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1262464805853361</v>
+        <v>0.4233679591151912</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2047801387197362</v>
+        <v>5.135363427243423</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1204811031349596</v>
+        <v>0.9060560943103231</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.006259542434651</v>
+        <v>4.418531381175067</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.263822533756821</v>
+        <v>1.681013035314933</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.008133655866459</v>
+        <v>0.03318728004501843</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.032264587201764</v>
+        <v>0.06918036668134761</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62243980126256</v>
+        <v>0.1330834678444263</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.328322949758636</v>
+        <v>0.06710002900440358</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.3391089227559433</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.02677780589124271</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.1949306916753765</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.1262464805853277</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.2047801387197354</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.1204811031349711</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>5.837101040643073</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.532933261738349</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9.89212403057382</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.972293414976843</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.236721685450954</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.04284318395723</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.9857317534965429</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.601853563175703</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.277381149353092</v>
       </c>
     </row>
     <row r="17">
@@ -2215,106 +2965,151 @@
         <v>64</v>
       </c>
       <c r="B17" t="n">
-        <v>1.071308468360282</v>
+        <v>39.31262966337232</v>
       </c>
       <c r="C17" t="n">
-        <v>4.693422989111981</v>
+        <v>1.071308468360268</v>
       </c>
       <c r="D17" t="n">
-        <v>1.401456306848656</v>
+        <v>74.49310423567907</v>
       </c>
       <c r="E17" t="n">
+        <v>4.693422989111985</v>
+      </c>
+      <c r="F17" t="n">
+        <v>62.51808845783727</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.401456306848653</v>
+      </c>
+      <c r="H17" t="n">
+        <v>70.20733897931497</v>
+      </c>
+      <c r="I17" t="n">
         <v>11.66113666102204</v>
       </c>
-      <c r="F17" t="n">
-        <v>1.20282027570587</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.270764583987216</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.401295945062245</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8667875665985131</v>
-      </c>
       <c r="J17" t="n">
-        <v>0.3784779191494644</v>
+        <v>7.204668538176678</v>
       </c>
       <c r="K17" t="n">
-        <v>1.617234377225461</v>
+        <v>1.202820275705861</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6847619189128485</v>
+        <v>26.77622269465471</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2467757602111794</v>
+        <v>1.270764583987215</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4608622618905088</v>
+        <v>6.834090891425496</v>
       </c>
       <c r="O17" t="n">
-        <v>1.016661628550568</v>
+        <v>1.401295945062247</v>
       </c>
       <c r="P17" t="n">
-        <v>1.402286923322332</v>
+        <v>5.640385370653641</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.980683763039865</v>
+        <v>0.8667875665985223</v>
       </c>
       <c r="R17" t="n">
-        <v>2.742540045171753</v>
+        <v>5.832669356257241</v>
       </c>
       <c r="S17" t="n">
-        <v>9.299355159883566</v>
+        <v>0.3784779191494764</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06576923947554573</v>
+        <v>5.239155670268182</v>
       </c>
       <c r="U17" t="n">
-        <v>0.02729921170970807</v>
+        <v>1.617234377225464</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1141007435491227</v>
+        <v>4.637872063738272</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1221071631659819</v>
+        <v>0.6847619189128343</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2009478152167689</v>
+        <v>5.144876321985925</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1628137030335363</v>
+        <v>0.2467757602111861</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1776604696013695</v>
+        <v>6.141893021191247</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.1497782931902975</v>
+        <v>0.4608622618905068</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1933509438833602</v>
+        <v>5.161506606161965</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1656692632016087</v>
+        <v>1.016661628550569</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.6336214116174603</v>
+        <v>4.968024513411917</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.261403947407627</v>
+        <v>1.402286923322337</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.265201047056749</v>
+        <v>0.06576923947554637</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.957962496667729</v>
+        <v>0.02729921170970771</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.146437027734458</v>
+        <v>0.1141007435491375</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.429425221617836</v>
+        <v>0.1221071631659884</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.2009478152167731</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.1628137030335429</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.1776604696013676</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.1497782931903059</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.1933509438833707</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.1656692632016181</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>6.548665866008854</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>2.48347691626401</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.142478750291799</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.6079535507579642</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.257902558014897</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.223574866618391</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.88709033709662</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.133590169942025</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.35687084645836</v>
       </c>
     </row>
     <row r="18">
@@ -2322,106 +3117,151 @@
         <v>68</v>
       </c>
       <c r="B18" t="n">
-        <v>11.47051912794459</v>
+        <v>79.45049124857367</v>
       </c>
       <c r="C18" t="n">
-        <v>4.91052034985893</v>
+        <v>11.4705191279446</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9801464071280156</v>
+        <v>74.90671314381244</v>
       </c>
       <c r="E18" t="n">
+        <v>4.910520349858926</v>
+      </c>
+      <c r="F18" t="n">
+        <v>62.83567815518516</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9801464071280064</v>
+      </c>
+      <c r="H18" t="n">
+        <v>69.84833342405319</v>
+      </c>
+      <c r="I18" t="n">
         <v>11.48530815395651</v>
       </c>
-      <c r="F18" t="n">
-        <v>1.174597259211549</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.117254716721649</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.9579715976072731</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.100258688517369</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.6212333838110126</v>
+        <v>6.731176821178986</v>
       </c>
       <c r="K18" t="n">
-        <v>1.182028510767857</v>
+        <v>1.17459725921155</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7101109789574787</v>
+        <v>26.18306320080902</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2896184661476464</v>
+        <v>1.117254716721655</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3690100236145754</v>
+        <v>6.77042852823546</v>
       </c>
       <c r="O18" t="n">
-        <v>1.019325333284931</v>
+        <v>0.9579715976072778</v>
       </c>
       <c r="P18" t="n">
-        <v>1.421955266306484</v>
+        <v>5.656754414242575</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.595546724971921</v>
+        <v>1.100258688517362</v>
       </c>
       <c r="R18" t="n">
-        <v>3.824043579574721</v>
+        <v>5.877534504231154</v>
       </c>
       <c r="S18" t="n">
-        <v>8.363730636674823</v>
+        <v>0.6212333838110059</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0291018920733028</v>
+        <v>5.048984822671668</v>
       </c>
       <c r="U18" t="n">
-        <v>0.05167218026115736</v>
+        <v>1.182028510767863</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2687490893077517</v>
+        <v>4.805786392024393</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1061347681300324</v>
+        <v>0.7101109789574789</v>
       </c>
       <c r="X18" t="n">
+        <v>5.106323371775392</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.2896184661476508</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.084956217750383</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.3690100236145669</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.204332178035302</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.019325333284927</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>5.005840390733299</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.421955266306479</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.02910189207330045</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.05167218026116543</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.2687490893077603</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.1061347681300483</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>0.2376779566300972</v>
       </c>
-      <c r="Y18" t="n">
-        <v>0.1530309604924726</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.2407526840114727</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.06091815725324561</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.2274680409212077</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.01928766575452634</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.12892889503359</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.5214083316910105</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.501478292357117</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0.6195641770620319</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.243557962323016</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.2424194068280272</v>
+      <c r="AK18" t="n">
+        <v>0.1530309604924791</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.2407526840114821</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.06091815725324232</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.2274680409212168</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.01928766575452333</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>5.179357881157704</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3.601974325935851</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>8.299581909714163</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.095765384126346</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.4574808483150331</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.350039526545951</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.5552022104908849</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3.116660410605341</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.2624848482205927</v>
       </c>
     </row>
     <row r="19">
@@ -2429,106 +3269,151 @@
         <v>72</v>
       </c>
       <c r="B19" t="n">
-        <v>1.408888907553773</v>
+        <v>40.40834163093888</v>
       </c>
       <c r="C19" t="n">
-        <v>4.850577584387187</v>
+        <v>1.40888890755377</v>
       </c>
       <c r="D19" t="n">
-        <v>1.420703292381402</v>
+        <v>73.92897935894825</v>
       </c>
       <c r="E19" t="n">
-        <v>12.11249126197809</v>
+        <v>4.85057758438719</v>
       </c>
       <c r="F19" t="n">
-        <v>1.297349283776954</v>
+        <v>28.96890002358575</v>
       </c>
       <c r="G19" t="n">
-        <v>1.212636818224579</v>
+        <v>1.420703292381403</v>
       </c>
       <c r="H19" t="n">
-        <v>1.021354572865863</v>
+        <v>68.26405376474685</v>
       </c>
       <c r="I19" t="n">
-        <v>1.108915170725991</v>
+        <v>12.1124912619781</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7114465297596937</v>
+        <v>6.470885375817009</v>
       </c>
       <c r="K19" t="n">
-        <v>1.184159160160056</v>
+        <v>1.29734928377696</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5273358219686742</v>
+        <v>26.62530638926651</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1117582686508204</v>
+        <v>1.212636818224588</v>
       </c>
       <c r="N19" t="n">
-        <v>0.08111606683956989</v>
+        <v>6.636704917182817</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6945282936648169</v>
+        <v>1.02135457286586</v>
       </c>
       <c r="P19" t="n">
-        <v>1.238343644542104</v>
+        <v>5.346899848788737</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.884542755516831</v>
+        <v>1.108915170725993</v>
       </c>
       <c r="R19" t="n">
-        <v>4.606479636254806</v>
+        <v>5.778646425372365</v>
       </c>
       <c r="S19" t="n">
-        <v>9.838336439555604</v>
+        <v>0.7114465297596905</v>
       </c>
       <c r="T19" t="n">
-        <v>0.05610699489883279</v>
+        <v>4.771147123352191</v>
       </c>
       <c r="U19" t="n">
-        <v>0.04186876605610038</v>
+        <v>1.184159160160054</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1390753975454639</v>
+        <v>5.069107682901736</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2241820399335872</v>
+        <v>0.5273358219686739</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1168299054279956</v>
+        <v>5.177625054930931</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1770696444786528</v>
+        <v>0.1117582686508178</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.1281694779504363</v>
+        <v>5.956598473924219</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1386967974605722</v>
+        <v>0.08111606683956407</v>
       </c>
       <c r="AB19" t="n">
+        <v>5.311573788392915</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.6945282936648162</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>5.324170641698703</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.238343644542094</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.05610699489884035</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.04186876605610677</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.1390753975454765</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.224182039933595</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.1168299054280052</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.1770696444786535</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.1281694779504357</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.1386967974605785</v>
+      </c>
+      <c r="AN19" t="n">
         <v>0.1891533200690425</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0.1232631772039041</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.012624341330073</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.68523962345765</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0.6831379252597487</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.666835579135882</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0.7015697263122334</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.790105065371073</v>
+      <c r="AO19" t="n">
+        <v>0.1232631772039079</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.639871585662656</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.395169209357349</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.726799198202407</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.9084803438561766</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.7254390843837897</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.5990984318066398</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.563234885052335</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.6413322115702984</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.710669485483205</v>
       </c>
     </row>
     <row r="20">
@@ -2536,106 +3421,151 @@
         <v>76</v>
       </c>
       <c r="B20" t="n">
-        <v>1.17645012069463</v>
+        <v>40.68155943103398</v>
       </c>
       <c r="C20" t="n">
-        <v>4.854424740642312</v>
+        <v>1.176450120694637</v>
       </c>
       <c r="D20" t="n">
-        <v>1.425431213559298</v>
+        <v>12.65708718548964</v>
       </c>
       <c r="E20" t="n">
-        <v>3.130786176843095</v>
+        <v>4.854424740642313</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9686961606248834</v>
+        <v>29.09838138773596</v>
       </c>
       <c r="G20" t="n">
-        <v>1.125301763002595</v>
+        <v>1.425431213559304</v>
       </c>
       <c r="H20" t="n">
-        <v>1.094719895230517</v>
+        <v>19.62474095870245</v>
       </c>
       <c r="I20" t="n">
-        <v>0.842337808608745</v>
+        <v>3.130786176843096</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5463291715779067</v>
+        <v>20.62130118505558</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7987550199050135</v>
+        <v>0.9686961606248832</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2465491529004007</v>
+        <v>27.51314939867594</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1888662580842805</v>
+        <v>1.125301763002585</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3475134701195133</v>
+        <v>7.274343764600401</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5850201617639063</v>
+        <v>1.094719895230516</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8318975283777639</v>
+        <v>5.507895708642386</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.58951888030557</v>
+        <v>0.8423378086087417</v>
       </c>
       <c r="R20" t="n">
-        <v>3.998943294090103</v>
+        <v>5.829398092040074</v>
       </c>
       <c r="S20" t="n">
-        <v>7.800136826332063</v>
+        <v>0.5463291715779048</v>
       </c>
       <c r="T20" t="n">
-        <v>0.05465650834293739</v>
+        <v>5.191406419243168</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1041812678915353</v>
+        <v>0.7987550199050112</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1906480291788564</v>
+        <v>4.967814087133953</v>
       </c>
       <c r="W20" t="n">
-        <v>0.06406467705432274</v>
+        <v>0.2465491529003996</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1957003945837374</v>
+        <v>5.215720904558282</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.3595483061422458</v>
+        <v>0.1888662580842889</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.05476333081590751</v>
+        <v>5.984379986139031</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.1147194616176133</v>
+        <v>0.3475134701195168</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.02275205557850456</v>
+        <v>5.465659593334457</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.120648141109494</v>
+        <v>0.585020161763909</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.8006561432959518</v>
+        <v>5.145347281317631</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.63916955523767</v>
+        <v>0.8318975283777689</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.8529743375926471</v>
+        <v>0.05465650834295269</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.5042259017873649</v>
+        <v>0.1041812678915393</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.291998361345333</v>
+        <v>0.1906480291788664</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.838075026901949</v>
+        <v>0.06406467705433495</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.195700394583747</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.3595483061422515</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.05476333081591065</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.1147194616176116</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.02275205557850209</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.1206481411095015</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.391963109787286</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.905406757874084</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7.801253247161562</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.7020375568829961</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.587341224729244</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.7606984755456284</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.574581497219014</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.26349459370093</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.846954433887693</v>
       </c>
     </row>
     <row r="21">
@@ -2643,106 +3573,151 @@
         <v>80</v>
       </c>
       <c r="B21" t="n">
-        <v>1.174485997075495</v>
+        <v>40.68334623986086</v>
       </c>
       <c r="C21" t="n">
+        <v>1.174485997075488</v>
+      </c>
+      <c r="D21" t="n">
+        <v>73.37240777047049</v>
+      </c>
+      <c r="E21" t="n">
         <v>4.896422694841183</v>
       </c>
-      <c r="D21" t="n">
-        <v>3.001023820756302</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
+        <v>19.87372935914146</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.001023820756301</v>
+      </c>
+      <c r="H21" t="n">
+        <v>65.88396872575078</v>
+      </c>
+      <c r="I21" t="n">
         <v>13.15164596357586</v>
       </c>
-      <c r="F21" t="n">
-        <v>1.474724239631525</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.215562705228266</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.313005754699243</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.8925208661451904</v>
-      </c>
       <c r="J21" t="n">
-        <v>0.7719668699344148</v>
+        <v>20.84329390559856</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4678182150797726</v>
+        <v>1.474724239631527</v>
       </c>
       <c r="L21" t="n">
-        <v>0.50960807852736</v>
+        <v>27.34938078666908</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1408638927730342</v>
+        <v>1.215562705228259</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3799757377574171</v>
+        <v>7.832348671778892</v>
       </c>
       <c r="O21" t="n">
+        <v>1.313005754699234</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.390426788597968</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.8925208661451908</v>
+      </c>
+      <c r="R21" t="n">
+        <v>5.696942293146082</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.7719668699344224</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.977240409379517</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.4678182150797778</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.891648038056212</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.5096080785273605</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.120831579346274</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.1408638927730281</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.67017844545525</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.3799757377574228</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.362438718355567</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.286586676355991</v>
       </c>
-      <c r="P21" t="n">
+      <c r="AD21" t="n">
+        <v>5.253062281452458</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.780810105948642</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.337327001771358</v>
-      </c>
-      <c r="R21" t="n">
-        <v>5.044462120852335</v>
-      </c>
-      <c r="S21" t="n">
-        <v>7.461450533145801</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.1643247434978379</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.05331280026237501</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.01464133722583996</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.1673168745948598</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.6047093795599749</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.3454568391556361</v>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AF21" t="n">
+        <v>0.1643247434978349</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.0533128002623663</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.01464133722582732</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.1673168745948675</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.6047093795599754</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.3454568391556437</v>
+      </c>
+      <c r="AL21" t="n">
         <v>0.2393130098138057</v>
       </c>
-      <c r="AA21" t="n">
-        <v>0.03943323770589262</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0.1859579689985589</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0.02770585201001393</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.158091007515321</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.8349349521570161</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.488373490974152</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.5424012101671094</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>3.209339187306389</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.343100509966143</v>
+      <c r="AM21" t="n">
+        <v>0.03943323770588729</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.1859579689985661</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.02770585201001921</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.332385958692934</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.97889007103215</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7.43167290988628</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.07793057625692</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.7827917648886669</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.521791352853818</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.6266677794748764</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.264444128252635</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.39531620192957</v>
       </c>
     </row>
     <row r="22">
@@ -2750,106 +3725,151 @@
         <v>84</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9203044028627401</v>
+        <v>41.44740792460152</v>
       </c>
       <c r="C22" t="n">
-        <v>6.949038791638357</v>
+        <v>0.9203044028627415</v>
       </c>
       <c r="D22" t="n">
-        <v>1.260341418312888</v>
+        <v>13.98609288398509</v>
       </c>
       <c r="E22" t="n">
-        <v>1.939749701422446</v>
+        <v>6.949038791638359</v>
       </c>
       <c r="F22" t="n">
-        <v>1.084687407531807</v>
+        <v>14.64982853361461</v>
       </c>
       <c r="G22" t="n">
-        <v>1.249098917070626</v>
+        <v>1.260341418312882</v>
       </c>
       <c r="H22" t="n">
-        <v>1.308031937825585</v>
+        <v>13.20011463703089</v>
       </c>
       <c r="I22" t="n">
-        <v>1.453623302164059</v>
+        <v>1.939749701422442</v>
       </c>
       <c r="J22" t="n">
-        <v>1.290013318707736</v>
+        <v>20.37195079947939</v>
       </c>
       <c r="K22" t="n">
-        <v>1.981789899238364</v>
+        <v>1.084687407531809</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1499572021625568</v>
+        <v>27.29176874981934</v>
       </c>
       <c r="M22" t="n">
-        <v>0.312827538144525</v>
+        <v>1.249098917070623</v>
       </c>
       <c r="N22" t="n">
+        <v>8.396807981053149</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.308031937825578</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5.143899092214846</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.453623302164046</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5.35947260015744</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.290013318707731</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4.791028009121129</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.981789899238358</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.966557050145292</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.1499572021625386</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.937773505975937</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.3128275381445225</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.593199992174112</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.37694347864441</v>
       </c>
-      <c r="O22" t="n">
+      <c r="AB22" t="n">
+        <v>5.443011008581961</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.298814852795958</v>
       </c>
-      <c r="P22" t="n">
-        <v>3.156377955768772</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.576555129260929</v>
-      </c>
-      <c r="R22" t="n">
-        <v>4.191282094347248</v>
-      </c>
-      <c r="S22" t="n">
-        <v>6.810515019400993</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.1611332853754696</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.1004499060319802</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.1455037902597981</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.06890401327778126</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.4997898355140536</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.4369505440737398</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.08920252424728348</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.1028786022334774</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.07686473964601657</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.08923877868041025</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.564476075833648</v>
+        <v>5.290664444851599</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.432370404037165</v>
+        <v>3.15637795576878</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.937762680023695</v>
+        <v>0.1611332853754673</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.9645074912866105</v>
+        <v>0.1004499060319769</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.648359423809368</v>
+        <v>0.1455037902598039</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.109654141977519</v>
+        <v>0.06890401327777219</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.4997898355140604</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.4369505440737397</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.08920252424728099</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.1028786022334801</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.07686473964602479</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.08923877868041731</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6.207911930140952</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.112019445485734</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>6.882325273546009</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.526766462356833</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.368463715103705</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.000988429681158</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.080594920594751</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.761893307168368</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>3.135550661617177</v>
       </c>
     </row>
     <row r="23">
@@ -2857,106 +3877,151 @@
         <v>88</v>
       </c>
       <c r="B23" t="n">
+        <v>76.85639173962795</v>
+      </c>
+      <c r="C23" t="n">
         <v>14.45655226299465</v>
       </c>
-      <c r="C23" t="n">
-        <v>3.797111329094343</v>
-      </c>
       <c r="D23" t="n">
-        <v>1.635993950492764</v>
+        <v>14.79800315765914</v>
       </c>
       <c r="E23" t="n">
-        <v>3.314470625609846</v>
+        <v>3.797111329094351</v>
       </c>
       <c r="F23" t="n">
-        <v>2.985420949101318</v>
+        <v>14.46965317079371</v>
       </c>
       <c r="G23" t="n">
-        <v>1.275454605240117</v>
+        <v>1.635993950492769</v>
       </c>
       <c r="H23" t="n">
-        <v>1.823853331001835</v>
+        <v>11.48071839503932</v>
       </c>
       <c r="I23" t="n">
-        <v>1.353187270089849</v>
+        <v>3.314470625609848</v>
       </c>
       <c r="J23" t="n">
-        <v>1.326926964128068</v>
+        <v>8.990609112244417</v>
       </c>
       <c r="K23" t="n">
-        <v>1.510660998564619</v>
+        <v>2.985420949101323</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1537602365600044</v>
+        <v>27.46227063515752</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4184549224827803</v>
+        <v>1.275454605240115</v>
       </c>
       <c r="N23" t="n">
-        <v>1.264509413808008</v>
+        <v>8.958333355126022</v>
       </c>
       <c r="O23" t="n">
-        <v>2.698743089266745</v>
+        <v>1.823853331001833</v>
       </c>
       <c r="P23" t="n">
-        <v>3.880226610829948</v>
+        <v>5.519589892326481</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.742678991954972</v>
+        <v>1.35318727008985</v>
       </c>
       <c r="R23" t="n">
-        <v>7.5184636237689</v>
+        <v>5.52843740919132</v>
       </c>
       <c r="S23" t="n">
-        <v>8.899171792489732</v>
+        <v>1.32692696412807</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09598232676533035</v>
+        <v>4.282291035486882</v>
       </c>
       <c r="U23" t="n">
-        <v>0.09894543069159457</v>
+        <v>1.510660998564624</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1231917255079662</v>
+        <v>4.973867249352007</v>
       </c>
       <c r="W23" t="n">
-        <v>0.281767878089996</v>
+        <v>0.1537602365599989</v>
       </c>
       <c r="X23" t="n">
+        <v>4.946781947063999</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.4184549224827916</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.397318656569394</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.264509413808006</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>5.41144363961414</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.698743089266748</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.533579381803717</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3.880226610829951</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.09598232676532856</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.09894543069159437</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.1231917255079605</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.28176787809</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>0.3119652186949546</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0.295402719682636</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.1041087462243655</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.16997415966261</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.02214233349653851</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.2406658961842156</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.14812635631238</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.305466878317165</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.319849076113445</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.247198930979558</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.033550549500826</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.753543327312078</v>
+      <c r="AK23" t="n">
+        <v>0.2954027196826372</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.1041087462243828</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.1699741596626167</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.02214233349654875</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.2406658961842211</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>2.409972683896837</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.488943802481657</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>9.028569597687145</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.073871886994619</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.2447102823869092</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.361721041487725</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.307063792401122</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.031997943205519</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.839376737980698</v>
       </c>
     </row>
     <row r="24">
@@ -2964,106 +4029,151 @@
         <v>92</v>
       </c>
       <c r="B24" t="n">
-        <v>14.92746627547988</v>
+        <v>76.3382911783157</v>
       </c>
       <c r="C24" t="n">
-        <v>5.079991017657425</v>
+        <v>14.92746627547989</v>
       </c>
       <c r="D24" t="n">
-        <v>3.611840871924675</v>
+        <v>16.11093185060325</v>
       </c>
       <c r="E24" t="n">
-        <v>3.596163354465562</v>
+        <v>5.079991017657422</v>
       </c>
       <c r="F24" t="n">
+        <v>11.40980183329806</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.611840871924673</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9.035558351313743</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.596163354465564</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10.38373855121628</v>
+      </c>
+      <c r="K24" t="n">
         <v>2.124921745321271</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.193366574167094</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.4973897553384</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.8612088884458897</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.8970035120206378</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.6199230632172508</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.4710557856212499</v>
+        <v>10.98581009372148</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3718078131727874</v>
+        <v>2.193366574167092</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8610360121419225</v>
+        <v>9.547524589385841</v>
       </c>
       <c r="O24" t="n">
-        <v>2.403915820441848</v>
+        <v>2.497389755338392</v>
       </c>
       <c r="P24" t="n">
-        <v>3.688163452716683</v>
+        <v>5.118466230559258</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.706074508187113</v>
+        <v>0.8612088884458913</v>
       </c>
       <c r="R24" t="n">
-        <v>6.719667115022081</v>
+        <v>5.292810603312302</v>
       </c>
       <c r="S24" t="n">
-        <v>6.684341586139861</v>
+        <v>0.8970035120206361</v>
       </c>
       <c r="T24" t="n">
+        <v>4.567458660914775</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.6199230632172458</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.997624639812192</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.4710557856212471</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5.065305193727464</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.3718078131727823</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.196426482408995</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.8610360121419111</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.424091749665573</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.40391582044185</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>5.809120025564902</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3.688163452716678</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0.06173838744710117</v>
       </c>
-      <c r="U24" t="n">
-        <v>0.1370857362534214</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.4350527736769197</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.3325007563162127</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AG24" t="n">
+        <v>0.1370857362534193</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.435052773676918</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.332500756316209</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>0.2115915074441406</v>
       </c>
-      <c r="Y24" t="n">
-        <v>0.5203752272622402</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AK24" t="n">
+        <v>0.5203752272622428</v>
+      </c>
+      <c r="AL24" t="n">
         <v>0.374698799771598</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0.1265641935384086</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AM24" t="n">
+        <v>0.1265641935384005</v>
+      </c>
+      <c r="AN24" t="n">
         <v>0.4106867493516732</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0.1467827094258485</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.191969667122421</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.312635120204309</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0.6137522634207129</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.082289788286995</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.861025547700592</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.721033221254275</v>
+      <c r="AO24" t="n">
+        <v>0.1467827094258443</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.469409522811365</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>6.569010480906613</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.588496286355892</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.217532665945126</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.265735207758853</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.6472179803753619</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.081753183770164</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.919903489687754</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2.708144732337085</v>
       </c>
     </row>
     <row r="25">
@@ -3071,106 +4181,151 @@
         <v>96</v>
       </c>
       <c r="B25" t="n">
-        <v>1.98036460523334</v>
+        <v>42.50830993517368</v>
       </c>
       <c r="C25" t="n">
-        <v>9.646413985315268</v>
+        <v>1.980364605233337</v>
       </c>
       <c r="D25" t="n">
-        <v>2.071416735827905</v>
+        <v>70.78681791992038</v>
       </c>
       <c r="E25" t="n">
+        <v>9.646413985315272</v>
+      </c>
+      <c r="F25" t="n">
+        <v>17.44042005304729</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.071416735827901</v>
+      </c>
+      <c r="H25" t="n">
+        <v>60.32686273795748</v>
+      </c>
+      <c r="I25" t="n">
         <v>17.0783764693466</v>
       </c>
-      <c r="F25" t="n">
-        <v>0.7689198844217424</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="J25" t="n">
+        <v>19.36802288890258</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.7689198844217404</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.71838830415682</v>
+      </c>
+      <c r="M25" t="n">
         <v>1.725258505599142</v>
       </c>
-      <c r="H25" t="n">
-        <v>3.245569224801301</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.9830194227481051</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.9344487194310482</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.6764240561177606</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.1087348729577047</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.3507547486629722</v>
-      </c>
       <c r="N25" t="n">
-        <v>1.018012478017337</v>
+        <v>9.699590637009765</v>
       </c>
       <c r="O25" t="n">
-        <v>2.768231282926528</v>
+        <v>3.245569224801303</v>
       </c>
       <c r="P25" t="n">
-        <v>4.725063122735155</v>
+        <v>5.127134026156591</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.726878900454446</v>
+        <v>0.9830194227481066</v>
       </c>
       <c r="R25" t="n">
-        <v>6.309869035317234</v>
+        <v>5.449862930351174</v>
       </c>
       <c r="S25" t="n">
-        <v>7.101729778461901</v>
+        <v>0.9344487194310519</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3250657629417381</v>
+        <v>4.670708137897031</v>
       </c>
       <c r="U25" t="n">
-        <v>0.293235930731028</v>
+        <v>0.6764240561177738</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5827412452820246</v>
+        <v>5.255091962152079</v>
       </c>
       <c r="W25" t="n">
-        <v>0.262000003555332</v>
+        <v>0.1087348729577077</v>
       </c>
       <c r="X25" t="n">
-        <v>0.7617966410064646</v>
+        <v>5.07009510899761</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5267121234962725</v>
+        <v>0.3507547486629821</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.2974432664923053</v>
+        <v>5.345149106766</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.1534176348680643</v>
+        <v>1.018012478017348</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.3067225225874379</v>
+        <v>4.933232463660079</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.250570934248366</v>
+        <v>2.768231282926537</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.503732815380524</v>
+        <v>5.959242092974151</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.475471729764706</v>
+        <v>4.725063122735152</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.8501123372277</v>
+        <v>0.3250657629417322</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.28883054340847</v>
+        <v>0.2932359307310313</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.630394734992618</v>
+        <v>0.5827412452820216</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.858033904559178</v>
+        <v>0.2620000035553396</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.7617966410064704</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.5267121234962647</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.2974432664922951</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.1534176348680683</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.3067225225874423</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.2505709342483609</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>4.540754076584178</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>6.258123509769446</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>7.053414877746966</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.482460590027736</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.398776408904257</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.818286582149561</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.291514787987172</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.604030102534654</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2.859276130153847</v>
       </c>
     </row>
     <row r="26">
@@ -3178,106 +4333,151 @@
         <v>100</v>
       </c>
       <c r="B26" t="n">
-        <v>16.64724461499078</v>
+        <v>76.00540930700653</v>
       </c>
       <c r="C26" t="n">
-        <v>8.732801071945472</v>
+        <v>16.64724461499077</v>
       </c>
       <c r="D26" t="n">
-        <v>1.943722123623095</v>
+        <v>35.96745838763864</v>
       </c>
       <c r="E26" t="n">
-        <v>16.91697351180601</v>
+        <v>8.732801071945469</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7174537685089117</v>
+        <v>17.37626704223698</v>
       </c>
       <c r="G26" t="n">
-        <v>1.675000697463686</v>
+        <v>1.943722123623089</v>
       </c>
       <c r="H26" t="n">
+        <v>60.11251605802642</v>
+      </c>
+      <c r="I26" t="n">
+        <v>16.916973511806</v>
+      </c>
+      <c r="J26" t="n">
+        <v>18.76621932543498</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.7174537685089076</v>
+      </c>
+      <c r="L26" t="n">
+        <v>25.82546532763526</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.675000697463684</v>
+      </c>
+      <c r="N26" t="n">
+        <v>23.09775466425759</v>
+      </c>
+      <c r="O26" t="n">
         <v>2.409879230881504</v>
       </c>
-      <c r="I26" t="n">
-        <v>1.34845236171591</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.182251044424328</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.19699104056734</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.4836356243488328</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.4679221240621986</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.28306325189391</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.077112192504227</v>
-      </c>
       <c r="P26" t="n">
-        <v>5.396844271415286</v>
+        <v>5.330337379005718</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.490069288981511</v>
+        <v>1.348452361715909</v>
       </c>
       <c r="R26" t="n">
-        <v>1.257655142881213</v>
+        <v>5.676260502817713</v>
       </c>
       <c r="S26" t="n">
-        <v>3.573557562767882</v>
+        <v>1.182251044424333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6480893081562301</v>
+        <v>5.801711476882922</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3296304384426472</v>
+        <v>1.196991040567335</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6187994785480457</v>
+        <v>5.86523296603537</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3014090630443096</v>
+        <v>0.4836356243488293</v>
       </c>
       <c r="X26" t="n">
-        <v>1.262929297285848</v>
+        <v>5.714684839289436</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5182386303982391</v>
+        <v>0.4679221240621937</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.2869987693390676</v>
+        <v>5.331462017255981</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.0545136293601844</v>
+        <v>1.283063251893913</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.2069153138096819</v>
+        <v>5.09878089328957</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.2567746048383187</v>
+        <v>3.077112192504233</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.243911652769608</v>
+        <v>5.976147366005168</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.023094316728378</v>
+        <v>5.396844271415291</v>
       </c>
       <c r="AF26" t="n">
-        <v>5.163830526196928</v>
+        <v>0.6480893081562367</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.45641683218352</v>
+        <v>0.3296304384426571</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.036135737011655</v>
+        <v>0.6187994785480522</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.55375102564489</v>
+        <v>0.3014090630443175</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.262929297285833</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.5182386303982218</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.2869987693390797</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.05451362936017254</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.2069153138096987</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.2567746048382955</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>7.211184181813564</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.331198574362709</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>3.652598525906802</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.155915405897725</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.9898665356503655</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>5.148970007241844</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.478687468069039</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5.025156136289949</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.561112144661729</v>
       </c>
     </row>
   </sheetData>
